--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_87_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_87_R9.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6618</v>
+        <v>5.4212</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6637</v>
+        <v>8.6905</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0019</v>
+        <v>-3.2693</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7956</v>
+        <v>7.1341</v>
       </c>
       <c r="H2" t="n">
-        <v>2.438</v>
+        <v>5.9296</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6424</v>
+        <v>1.2045</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0971</v>
+        <v>10.2323</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5781</v>
+        <v>6.0266</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5189</v>
+        <v>4.2057</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.3015</v>
+        <v>-3.0982</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1401</v>
+        <v>-0.097</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1613</v>
+        <v>-3.0012</v>
       </c>
       <c r="P2" t="n">
-        <v>3.0154</v>
+        <v>0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2473</v>
+        <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0649</v>
+        <v>-1.1046</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7986</v>
+        <v>-0.2946</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2662</v>
+        <v>-0.8101</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3267</v>
+        <v>3.8094</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8648</v>
+        <v>3.6769</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.5381</v>
+        <v>0.1325</v>
       </c>
       <c r="G3" t="n">
-        <v>7.1341</v>
+        <v>1.7956</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9296</v>
+        <v>2.438</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2045</v>
+        <v>-0.6424</v>
       </c>
       <c r="J3" t="n">
-        <v>10.2323</v>
+        <v>4.0971</v>
       </c>
       <c r="K3" t="n">
-        <v>6.0266</v>
+        <v>2.5781</v>
       </c>
       <c r="L3" t="n">
-        <v>4.2057</v>
+        <v>1.5189</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0982</v>
+        <v>-2.3015</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.097</v>
+        <v>-0.1401</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.0012</v>
+        <v>-2.1613</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>3.0154</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7834</v>
+        <v>3.2473</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.1991</v>
+        <v>0.2124</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1202</v>
+        <v>-0.1883</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0789</v>
+        <v>0.4007</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1444</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4165</v>
+        <v>-0.4593</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7964</v>
+        <v>0.0887</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.38</v>
+        <v>-0.548</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0335</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0556</v>
+        <v>0.1799</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2072</v>
+        <v>0.4995</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1516</v>
+        <v>-0.3196</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3923</v>
+        <v>-0.4691</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4308</v>
+        <v>0.3972</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4061</v>
@@ -844,13 +844,13 @@
         <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6278</v>
+        <v>-0.7046</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6247</v>
+        <v>-0.668</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0031</v>
+        <v>-0.0367</v>
       </c>
       <c r="V5" t="n">
         <v>-1.214</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>S. LARKIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5037</v>
+        <v>-1.2134</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1598</v>
+        <v>-2.2155</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.344</v>
+        <v>1.0021</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8506</v>
+        <v>-1.811</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0108</v>
+        <v>1.3444</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8399</v>
+        <v>-3.1554</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7863</v>
+        <v>1.1336</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3381</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7863</v>
+        <v>-0.2045</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0643</v>
+        <v>-2.9446</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0108</v>
+        <v>0.0063</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0535</v>
+        <v>-2.9509</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>3.7112</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0448</v>
+        <v>-0.5621</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3734</v>
+        <v>-0.7976</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3286</v>
+        <v>0.2355</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. LARKIN</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3496</v>
+        <v>-1.571</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3517</v>
+        <v>-1.1598</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0021</v>
+        <v>-0.4112</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.811</v>
+        <v>-0.8506</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3444</v>
+        <v>-0.0108</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.1554</v>
+        <v>-0.8399</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1336</v>
+        <v>-0.7863</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3381</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2045</v>
+        <v>-0.7863</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9446</v>
+        <v>-0.0643</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0063</v>
+        <v>-0.0108</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.9509</v>
+        <v>-0.0535</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7112</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6983</v>
+        <v>-0.112</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.9338</v>
+        <v>-0.3734</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2355</v>
+        <v>0.2614</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6189</v>
+        <v>-2.6292</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6571</v>
+        <v>-2.9363</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0382</v>
+        <v>0.3071</v>
       </c>
       <c r="G8" t="n">
         <v>-4.1443</v>
@@ -1078,13 +1078,13 @@
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0615</v>
+        <v>0.0512</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6097</v>
+        <v>0.3306</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5482</v>
+        <v>-0.2794</v>
       </c>
       <c r="V8" t="n">
         <v>0.5361</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.1012</v>
+        <v>-4.8653</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9825</v>
+        <v>-3.7466</v>
       </c>
       <c r="F9" t="n">
         <v>-1.1187</v>
@@ -1156,10 +1156,10 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1677</v>
+        <v>-0.9318</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U9" t="n">
         <v>-0.5702</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.4472</v>
+        <v>-6.6578</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.8095</v>
+        <v>-5.6168</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6377</v>
+        <v>-1.041</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6236</v>
@@ -1234,13 +1234,13 @@
         <v>3.4793</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2179</v>
+        <v>-0.4285</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9313</v>
+        <v>-0.7387</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7134</v>
+        <v>0.3102</v>
       </c>
       <c r="V10" t="n">
         <v>-1.214</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.007899999999999</v>
+        <v>-8.634500000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.458799999999998</v>
+        <v>-4.085299999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5493</v>
+        <v>-4.549300000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-4.5688</v>
@@ -1312,13 +1312,13 @@
         <v>19.716</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.7736</v>
+        <v>-3.4001</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.9654</v>
+        <v>-2.592</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8083</v>
+        <v>-0.8082</v>
       </c>
       <c r="V11" t="n">
         <v>-6.4643</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.9317</v>
+        <v>8.150499999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>6.8358</v>
+        <v>6.9537</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0959</v>
+        <v>1.1967</v>
       </c>
       <c r="G12" t="n">
         <v>7.7438</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5074</v>
+        <v>0.7262</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2047</v>
+        <v>0.3227</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3027</v>
+        <v>0.4035</v>
       </c>
       <c r="V12" t="n">
         <v>1.0722</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3764</v>
+        <v>6.646</v>
       </c>
       <c r="E13" t="n">
-        <v>6.1532</v>
+        <v>6.3891</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2233</v>
+        <v>0.2569</v>
       </c>
       <c r="G13" t="n">
         <v>3.2355</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2175</v>
+        <v>0.0521</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5149</v>
+        <v>-0.279</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2974</v>
+        <v>0.331</v>
       </c>
       <c r="V13" t="n">
         <v>3.3584</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0597</v>
+        <v>3.2684</v>
       </c>
       <c r="E14" t="n">
-        <v>2.256</v>
+        <v>2.6099</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8037</v>
+        <v>0.6585</v>
       </c>
       <c r="G14" t="n">
         <v>0.7903</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3053</v>
+        <v>0.514</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1766</v>
+        <v>0.1772</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4819</v>
+        <v>0.3367</v>
       </c>
       <c r="V14" t="n">
         <v>2.428</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.807</v>
+        <v>2.5977</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7426</v>
+        <v>2.0964</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0644</v>
+        <v>0.5013</v>
       </c>
       <c r="G15" t="n">
         <v>1.2967</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2577</v>
+        <v>-0.467</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5935</v>
+        <v>-0.1566</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7166</v>
+        <v>1.2835</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2755</v>
+        <v>0.4498</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4411</v>
+        <v>0.8336</v>
       </c>
       <c r="G16" t="n">
         <v>0.0618</v>
@@ -1702,13 +1702,13 @@
         <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.959</v>
+        <v>0.5258</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3566</v>
+        <v>0.5309</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3976</v>
+        <v>-0.005</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.3922</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6237</v>
+        <v>0.2698</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0552</v>
+        <v>0.1224</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2349</v>
@@ -1780,13 +1780,13 @@
         <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6818</v>
+        <v>0.3951</v>
       </c>
       <c r="T17" t="n">
-        <v>0.637</v>
+        <v>0.2831</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8250999999999999</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>-1.0574</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2324</v>
+        <v>0.2888</v>
       </c>
       <c r="G18" t="n">
         <v>-1.608</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6954</v>
+        <v>0.7519</v>
       </c>
       <c r="T18" t="n">
         <v>0.1968</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4986</v>
+        <v>0.5551</v>
       </c>
       <c r="V18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7932</v>
+        <v>-2.2508</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4159</v>
+        <v>-3.1297</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6227</v>
+        <v>0.8789</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3337</v>
+        <v>-2.0661</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.139</v>
+        <v>-0.9351</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4727</v>
+        <v>-1.131</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0571</v>
+        <v>-1.8836</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1611</v>
+        <v>-0.7023</v>
       </c>
       <c r="L19" t="n">
-        <v>2.2182</v>
+        <v>-1.1813</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7234</v>
+        <v>-0.1825</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9779</v>
+        <v>-0.2327</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2545</v>
+        <v>0.0502</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.9432</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.7988</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.2792</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8883</v>
+        <v>-0.0863</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4906</v>
+        <v>0.3655</v>
       </c>
       <c r="V19" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7152</v>
+        <v>-2.263</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9123</v>
+        <v>-3.18</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1971</v>
+        <v>0.917</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2991</v>
+        <v>0.3337</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5005</v>
+        <v>-2.139</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2014</v>
+        <v>2.4727</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2559</v>
+        <v>2.0571</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2163</v>
+        <v>-0.1611</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4722</v>
+        <v>2.2182</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.555</v>
+        <v>-1.7234</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2842</v>
+        <v>-1.9779</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2708</v>
+        <v>0.2545</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.7834</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.639</v>
+        <v>-5.7988</v>
       </c>
       <c r="R20" t="n">
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4394</v>
+        <v>0.1325</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4708</v>
+        <v>-0.6524</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9687</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0308</v>
+        <v>-3.3168</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4835</v>
+        <v>-2.8786</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4527</v>
+        <v>-0.4382</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0661</v>
+        <v>-3.685</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9351</v>
+        <v>-1.1152</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.131</v>
+        <v>-2.5698</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.8836</v>
+        <v>-3.095</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7023</v>
+        <v>-0.7359</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1813</v>
+        <v>-2.359</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1825</v>
+        <v>-0.59</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2327</v>
+        <v>-0.3792</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0502</v>
+        <v>-0.2108</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5008</v>
+        <v>0.4404</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4402</v>
+        <v>0.2164</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0606</v>
+        <v>0.224</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.1982</v>
+        <v>-3.9448</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4684</v>
+        <v>-3.9739</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7299</v>
+        <v>0.0291</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.685</v>
+        <v>-1.2991</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1152</v>
+        <v>-2.5005</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5698</v>
+        <v>1.2014</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.095</v>
+        <v>0.2559</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7359</v>
+        <v>-1.2163</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.359</v>
+        <v>1.4722</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.59</v>
+        <v>-1.555</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3792</v>
+        <v>-1.2842</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2108</v>
+        <v>-0.2708</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4639</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4411</v>
+        <v>1.2098</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3734</v>
+        <v>0.4092</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0677</v>
+        <v>0.8006</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.0078</v>
+        <v>9.7943</v>
       </c>
       <c r="E23" t="n">
-        <v>4.549300000000001</v>
+        <v>4.549100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>4.458600000000001</v>
+        <v>5.244999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>4.5687</v>
+        <v>4.568700000000001</v>
       </c>
       <c r="H23" t="n">
         <v>-8.564399999999999</v>
@@ -2224,7 +2224,7 @@
         <v>14.3119</v>
       </c>
       <c r="K23" t="n">
-        <v>0.07609999999999995</v>
+        <v>0.07610000000000028</v>
       </c>
       <c r="L23" t="n">
         <v>14.2358</v>
@@ -2248,16 +2248,16 @@
         <v>13.9173</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7735</v>
+        <v>4.56</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8083000000000002</v>
+        <v>0.8082000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>2.9653</v>
+        <v>3.751600000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>6.464299999999999</v>
+        <v>6.4643</v>
       </c>
       <c r="W23" t="n">
         <v>9.1448</v>
